--- a/hira_material_automation/output/monthly/202601_202607__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__all_suture_anchor__040021__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04T22:02:17</t>
+          <t>2026-07-14T22:02:09</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>91c9f1d7196bcf9750da966c9d940a15925ec6370a37c6bfcb3d432a317901be</t>
+          <t>48e6ae0ee07d64889735fd3d164336444fa9234ab7e6946c3373c636f0ce4c73</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202607__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__all_suture_anchor__040021__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14T22:02:09</t>
+          <t>2026-07-24T22:09:03</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48e6ae0ee07d64889735fd3d164336444fa9234ab7e6946c3373c636f0ce4c73</t>
+          <t>39f47c383d90bccf3f1594f74c8fe3f77ab0ac2aa16e82642c177240b0a3e989</t>
         </is>
       </c>
     </row>
